--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92537581751</v>
+        <v>46157.93111098927</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93111098927</v>
+        <v>46157.9336621589</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9336621589</v>
+        <v>46157.93668733112</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93668733112</v>
+        <v>46158.28192760902</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28192760902</v>
+        <v>46158.29714366452</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29714366452</v>
+        <v>46158.29788244139</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29788244139</v>
+        <v>46158.33354228835</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33354228835</v>
+        <v>46158.37209704857</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/1. АвтоТехЦентр (ИП Петраш Г.М.)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37209704857</v>
+        <v>46158.3726685086</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
